--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -24792,47 +24792,47 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17125360</t>
         </is>
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>439 - BOSQUE CARANDÁ</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Avenida PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>25/08/2026 09:35</t>
         </is>
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>25/08/2026 09:57</t>
         </is>
       </c>
       <c r="J12" s="29" t="n">
@@ -24842,47 +24842,47 @@
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>17125360</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
-          <t>439 - BOSQUE CARANDÁ</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E13" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
-          <t>Avenida PERPETUO SOCORRO</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>03 - OU</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:35</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I13" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:57</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J13" s="29" t="n">
@@ -25042,7 +25042,7 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
@@ -25052,37 +25052,37 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17098947</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>75 - R</t>
         </is>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>24/08/2026 09:26</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>24/08/2026 09:46</t>
         </is>
       </c>
       <c r="J17" s="29" t="n">
@@ -25142,47 +25142,47 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>17112709</t>
+          <t>17195999</t>
         </is>
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - R</t>
+          <t>843 - R</t>
         </is>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:00</t>
+          <t>28/08/2026 08:55</t>
         </is>
       </c>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:20</t>
+          <t>28/08/2026 09:15</t>
         </is>
       </c>
       <c r="J19" s="29" t="n">
@@ -25192,7 +25192,7 @@
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
@@ -25202,37 +25202,37 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>17098947</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G20" s="29" t="inlineStr">
         <is>
-          <t>75 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H20" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:26</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I20" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:46</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J20" s="29" t="n">
@@ -25242,47 +25242,47 @@
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>17195999</t>
+          <t>17112709</t>
         </is>
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>843 - R</t>
+          <t>295 - 1 - R</t>
         </is>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:55</t>
+          <t>24/08/2026 15:00</t>
         </is>
       </c>
       <c r="I21" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:15</t>
+          <t>24/08/2026 15:20</t>
         </is>
       </c>
       <c r="J21" s="29" t="n">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
@@ -25417,22 +25417,22 @@
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J24" s="29" t="n">
@@ -25492,47 +25492,47 @@
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>17184336</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>1391 - R</t>
         </is>
       </c>
       <c r="H26" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>27/08/2026 13:23</t>
         </is>
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>27/08/2026 13:41</t>
         </is>
       </c>
       <c r="J26" s="29" t="n">
@@ -25542,47 +25542,47 @@
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H27" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I27" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J27" s="29" t="n">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
@@ -25617,22 +25617,22 @@
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -25702,7 +25702,7 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>17184336</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D30" s="29" t="inlineStr">
@@ -25712,27 +25712,27 @@
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>1391 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:23</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I30" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:41</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J30" s="29" t="n">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>17098963</t>
+          <t>17195900</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
@@ -25812,27 +25812,27 @@
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Rua ARINO MOREIRA</t>
+          <t>Rua 13 DE SETEMBRO</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>39 - R</t>
+          <t>1502 - R</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:46</t>
+          <t>28/08/2026 14:53</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>28/08/2026 15:10</t>
         </is>
       </c>
       <c r="J32" s="29" t="n">
@@ -25842,7 +25842,7 @@
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
@@ -25852,37 +25852,37 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>17195900</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>Rua 13 DE SETEMBRO</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>1502 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:53</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I33" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 15:10</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J33" s="29" t="n">
@@ -25892,7 +25892,7 @@
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
@@ -25902,37 +25902,37 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17098963</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua ARINO MOREIRA</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>39 - R</t>
         </is>
       </c>
       <c r="H34" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>24/08/2026 15:46</t>
         </is>
       </c>
       <c r="I34" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="J34" s="29" t="n">
@@ -26042,7 +26042,7 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
@@ -26052,37 +26052,37 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>17098957</t>
+          <t>17178582</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua ROSA AMARELA</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>258 - R</t>
+          <t>305 - R</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:31</t>
+          <t>27/08/2026 09:33</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>27/08/2026 09:49</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>17098959</t>
+          <t>17098957</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
@@ -26122,17 +26122,17 @@
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>332 - R</t>
+          <t>258 - R</t>
         </is>
       </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:05</t>
+          <t>24/08/2026 14:31</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:21</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="J38" s="29" t="n">
@@ -26142,7 +26142,7 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
@@ -26152,37 +26152,37 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17178582</t>
+          <t>17098958</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AMARELA</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>305 - R</t>
+          <t>258 - 2 - OU</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 09:33</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 09:49</t>
+          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -26202,7 +26202,7 @@
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17098958</t>
+          <t>17098959</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
@@ -26222,17 +26222,17 @@
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>258 - 2 - OU</t>
+          <t>332 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>24/08/2026 15:05</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:03</t>
+          <t>24/08/2026 15:21</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">

--- a/data/historico/semana_321.xlsx
+++ b/data/historico/semana_321.xlsx
@@ -5248,7 +5248,7 @@
       </c>
       <c r="B7" s="41" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C7" s="41" t="inlineStr">
